--- a/excel/NetPix Ad Performance Metrics.xlsx
+++ b/excel/NetPix Ad Performance Metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e021863b747904f7/Documents/Data Analyst Projects/netflix-ad-performance-analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{0F910B5B-4D03-4626-967B-49B53062B46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5D8EB95-37D2-48A8-9E8C-8EED4C49F20C}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{0F910B5B-4D03-4626-967B-49B53062B46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFD8C676-8987-46EA-B023-A23FE54DFB34}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{F6B82202-03F3-4835-B18B-DEF1DC2C0D8E}"/>
   </bookViews>
@@ -226,6 +226,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,7 +552,8 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="23.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="23.26953125" style="2"/>
+    <col min="1" max="1" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="23.26953125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
